--- a/public/template_excel/import_user.xlsx
+++ b/public/template_excel/import_user.xlsx
@@ -8,16 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\FESP\fe-service-portal\public\template_excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED96F3D-70E9-4723-9915-6766F1DD75E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13C27778-B031-484C-A138-FB6112C30C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="users" sheetId="1" r:id="rId1"/>
     <sheet name="shift" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">users!$A$1:$M$2</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">users!$A$1:$O$2</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>stt</t>
   </si>
@@ -68,6 +68,12 @@
   </si>
   <si>
     <t>bo_phan</t>
+  </si>
+  <si>
+    <t>email</t>
+  </si>
+  <si>
+    <t>so_dien_thoai</t>
   </si>
 </sst>
 </file>
@@ -588,7 +594,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.5703125" customWidth="1"/>
@@ -602,11 +608,11 @@
     <col min="9" max="9" width="21.140625" customWidth="1"/>
     <col min="10" max="10" width="14.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="16.28515625" customWidth="1"/>
-    <col min="13" max="13" width="24.42578125" customWidth="1"/>
+    <col min="12" max="14" width="16.28515625" customWidth="1"/>
+    <col min="15" max="15" width="24.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="27.75" customHeight="1">
+    <row r="1" spans="1:15" ht="27.75" customHeight="1">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -644,10 +650,16 @@
         <v>9</v>
       </c>
       <c r="M1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="26.25" customHeight="1">
+    <row r="2" spans="1:15" ht="26.25" customHeight="1">
       <c r="A2" s="13"/>
       <c r="B2" s="12"/>
       <c r="C2" s="16"/>
@@ -660,9 +672,11 @@
       <c r="J2" s="16"/>
       <c r="K2" s="10"/>
       <c r="L2" s="9"/>
-      <c r="M2" s="5"/>
-    </row>
-    <row r="3" spans="1:13" ht="26.25" customHeight="1">
+      <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
+      <c r="O2" s="5"/>
+    </row>
+    <row r="3" spans="1:15" ht="26.25" customHeight="1">
       <c r="A3" s="4"/>
       <c r="B3" s="12"/>
       <c r="C3" s="8"/>
@@ -675,9 +689,11 @@
       <c r="J3" s="8"/>
       <c r="K3" s="10"/>
       <c r="L3" s="9"/>
-      <c r="M3" s="5"/>
-    </row>
-    <row r="4" spans="1:13" ht="18.75">
+      <c r="M3" s="9"/>
+      <c r="N3" s="9"/>
+      <c r="O3" s="5"/>
+    </row>
+    <row r="4" spans="1:15" ht="18.75">
       <c r="A4" s="4"/>
       <c r="B4" s="12"/>
       <c r="C4" s="8"/>
@@ -690,9 +706,11 @@
       <c r="J4" s="8"/>
       <c r="K4" s="10"/>
       <c r="L4" s="9"/>
-      <c r="M4" s="5"/>
-    </row>
-    <row r="5" spans="1:13" ht="18.75">
+      <c r="M4" s="9"/>
+      <c r="N4" s="9"/>
+      <c r="O4" s="5"/>
+    </row>
+    <row r="5" spans="1:15" ht="18.75">
       <c r="A5" s="4"/>
       <c r="B5" s="12"/>
       <c r="C5" s="8"/>
@@ -705,9 +723,11 @@
       <c r="J5" s="8"/>
       <c r="K5" s="10"/>
       <c r="L5" s="9"/>
-      <c r="M5" s="5"/>
-    </row>
-    <row r="6" spans="1:13" ht="18.75">
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="5"/>
+    </row>
+    <row r="6" spans="1:15" ht="18.75">
       <c r="A6" s="4"/>
       <c r="B6" s="12"/>
       <c r="C6" s="8"/>
@@ -720,9 +740,11 @@
       <c r="J6" s="8"/>
       <c r="K6" s="10"/>
       <c r="L6" s="9"/>
-      <c r="M6" s="5"/>
-    </row>
-    <row r="7" spans="1:13" ht="18.75">
+      <c r="M6" s="9"/>
+      <c r="N6" s="9"/>
+      <c r="O6" s="5"/>
+    </row>
+    <row r="7" spans="1:15" ht="18.75">
       <c r="A7" s="4"/>
       <c r="B7" s="12"/>
       <c r="C7" s="8"/>
@@ -735,9 +757,11 @@
       <c r="J7" s="8"/>
       <c r="K7" s="10"/>
       <c r="L7" s="9"/>
-      <c r="M7" s="5"/>
-    </row>
-    <row r="8" spans="1:13" ht="18.75">
+      <c r="M7" s="9"/>
+      <c r="N7" s="9"/>
+      <c r="O7" s="5"/>
+    </row>
+    <row r="8" spans="1:15" ht="18.75">
       <c r="A8" s="4"/>
       <c r="B8" s="12"/>
       <c r="C8" s="8"/>
@@ -750,9 +774,11 @@
       <c r="J8" s="8"/>
       <c r="K8" s="10"/>
       <c r="L8" s="9"/>
-      <c r="M8" s="5"/>
-    </row>
-    <row r="9" spans="1:13" ht="18.75">
+      <c r="M8" s="9"/>
+      <c r="N8" s="9"/>
+      <c r="O8" s="5"/>
+    </row>
+    <row r="9" spans="1:15" ht="18.75">
       <c r="A9" s="4"/>
       <c r="B9" s="12"/>
       <c r="C9" s="8"/>
@@ -765,9 +791,11 @@
       <c r="J9" s="8"/>
       <c r="K9" s="10"/>
       <c r="L9" s="9"/>
-      <c r="M9" s="5"/>
-    </row>
-    <row r="10" spans="1:13" ht="18.75">
+      <c r="M9" s="9"/>
+      <c r="N9" s="9"/>
+      <c r="O9" s="5"/>
+    </row>
+    <row r="10" spans="1:15" ht="18.75">
       <c r="A10" s="4"/>
       <c r="B10" s="12"/>
       <c r="C10" s="8"/>
@@ -780,9 +808,11 @@
       <c r="J10" s="8"/>
       <c r="K10" s="10"/>
       <c r="L10" s="9"/>
-      <c r="M10" s="5"/>
-    </row>
-    <row r="11" spans="1:13" ht="18.75">
+      <c r="M10" s="9"/>
+      <c r="N10" s="9"/>
+      <c r="O10" s="5"/>
+    </row>
+    <row r="11" spans="1:15" ht="18.75">
       <c r="A11" s="4"/>
       <c r="B11" s="12"/>
       <c r="C11" s="8"/>
@@ -795,9 +825,11 @@
       <c r="J11" s="8"/>
       <c r="K11" s="10"/>
       <c r="L11" s="9"/>
-      <c r="M11" s="5"/>
-    </row>
-    <row r="12" spans="1:13" ht="18.75">
+      <c r="M11" s="9"/>
+      <c r="N11" s="9"/>
+      <c r="O11" s="5"/>
+    </row>
+    <row r="12" spans="1:15" ht="18.75">
       <c r="A12" s="4"/>
       <c r="B12" s="12"/>
       <c r="C12" s="8"/>
@@ -810,9 +842,11 @@
       <c r="J12" s="8"/>
       <c r="K12" s="10"/>
       <c r="L12" s="9"/>
-      <c r="M12" s="5"/>
-    </row>
-    <row r="13" spans="1:13" ht="18.75">
+      <c r="M12" s="9"/>
+      <c r="N12" s="9"/>
+      <c r="O12" s="5"/>
+    </row>
+    <row r="13" spans="1:15" ht="18.75">
       <c r="A13" s="4"/>
       <c r="B13" s="12"/>
       <c r="C13" s="8"/>
@@ -825,10 +859,12 @@
       <c r="J13" s="8"/>
       <c r="K13" s="10"/>
       <c r="L13" s="9"/>
-      <c r="M13" s="5"/>
+      <c r="M13" s="9"/>
+      <c r="N13" s="9"/>
+      <c r="O13" s="5"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:O3" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="B3:B13">
     <cfRule type="duplicateValues" dxfId="1" priority="1"/>
   </conditionalFormatting>
